--- a/artfynd/A 55825-2023 artfynd.xlsx
+++ b/artfynd/A 55825-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55825-2023 artfynd.xlsx
+++ b/artfynd/A 55825-2023 artfynd.xlsx
@@ -2784,10 +2784,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117764531</v>
+        <v>117764571</v>
       </c>
       <c r="B20" t="n">
-        <v>97753</v>
+        <v>57303</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2796,55 +2796,56 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>500 m sso Horssjön (Tärnanområdet), Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>688383</v>
+        <v>688385</v>
       </c>
       <c r="R20" t="n">
-        <v>6609174</v>
+        <v>6609183</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2873,7 +2874,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2883,7 +2884,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2914,7 +2915,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117764517</v>
+        <v>117765296</v>
       </c>
       <c r="B21" t="n">
         <v>56499</v>
@@ -2959,10 +2960,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>688385</v>
+        <v>688444</v>
       </c>
       <c r="R21" t="n">
-        <v>6609176</v>
+        <v>6609199</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2994,7 +2995,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3004,7 +3005,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3035,10 +3036,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117765296</v>
+        <v>117764308</v>
       </c>
       <c r="B22" t="n">
-        <v>56499</v>
+        <v>8405</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3051,42 +3052,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>500 m sso Horssjön (Tärnanområdet), Upl</t>
+          <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>688444</v>
+        <v>688318</v>
       </c>
       <c r="R22" t="n">
-        <v>6609199</v>
+        <v>6609079</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3115,7 +3116,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3125,7 +3126,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3156,10 +3157,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117764762</v>
+        <v>117764531</v>
       </c>
       <c r="B23" t="n">
-        <v>8416</v>
+        <v>97753</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3172,27 +3173,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3201,10 +3211,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>688452</v>
+        <v>688383</v>
       </c>
       <c r="R23" t="n">
-        <v>6609271</v>
+        <v>6609174</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3236,7 +3246,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3246,7 +3256,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3277,10 +3287,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117764161</v>
+        <v>117764382</v>
       </c>
       <c r="B24" t="n">
-        <v>57303</v>
+        <v>90499</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3293,39 +3303,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>688348</v>
+        <v>688339</v>
       </c>
       <c r="R24" t="n">
-        <v>6609056</v>
+        <v>6609152</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3357,7 +3362,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3367,7 +3372,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3398,10 +3403,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117763847</v>
+        <v>117764101</v>
       </c>
       <c r="B25" t="n">
-        <v>56499</v>
+        <v>43657</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3414,42 +3419,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>101735</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>500 m sso Horssjön (Tärnanområdet), Upl</t>
+          <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>688345</v>
+        <v>688365</v>
       </c>
       <c r="R25" t="n">
-        <v>6609113</v>
+        <v>6609080</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3478,7 +3483,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3488,7 +3493,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3519,10 +3524,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117764465</v>
+        <v>117765426</v>
       </c>
       <c r="B26" t="n">
-        <v>8416</v>
+        <v>79098</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3531,46 +3536,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>688352</v>
+        <v>688454</v>
       </c>
       <c r="R26" t="n">
-        <v>6609177</v>
+        <v>6609165</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3640,10 +3640,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117763585</v>
+        <v>117764420</v>
       </c>
       <c r="B27" t="n">
-        <v>57303</v>
+        <v>8405</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3652,31 +3652,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>688392</v>
+        <v>688352</v>
       </c>
       <c r="R27" t="n">
-        <v>6609033</v>
+        <v>6609177</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3761,10 +3761,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117764129</v>
+        <v>117766609</v>
       </c>
       <c r="B28" t="n">
-        <v>96791</v>
+        <v>79098</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3773,25 +3773,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>688355</v>
+        <v>688479</v>
       </c>
       <c r="R28" t="n">
-        <v>6609075</v>
+        <v>6609210</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3877,10 +3877,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117764300</v>
+        <v>117764465</v>
       </c>
       <c r="B29" t="n">
-        <v>96791</v>
+        <v>8416</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3893,34 +3893,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>688317</v>
+        <v>688352</v>
       </c>
       <c r="R29" t="n">
-        <v>6609078</v>
+        <v>6609177</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3952,7 +3957,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3962,7 +3967,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3993,10 +3998,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117764382</v>
+        <v>117763595</v>
       </c>
       <c r="B30" t="n">
-        <v>90499</v>
+        <v>8416</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4005,38 +4010,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>688339</v>
+        <v>688398</v>
       </c>
       <c r="R30" t="n">
-        <v>6609152</v>
+        <v>6609030</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4068,7 +4078,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4078,7 +4088,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4109,10 +4119,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117764308</v>
+        <v>117764562</v>
       </c>
       <c r="B31" t="n">
-        <v>8405</v>
+        <v>97756</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4125,27 +4135,32 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106554</v>
+        <v>223597</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4154,13 +4169,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>688318</v>
+        <v>688381</v>
       </c>
       <c r="R31" t="n">
-        <v>6609079</v>
+        <v>6609183</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4189,7 +4204,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4199,7 +4214,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4230,10 +4245,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117763595</v>
+        <v>117764161</v>
       </c>
       <c r="B32" t="n">
-        <v>8416</v>
+        <v>57303</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4242,31 +4257,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4275,10 +4290,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>688398</v>
+        <v>688348</v>
       </c>
       <c r="R32" t="n">
-        <v>6609030</v>
+        <v>6609056</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4310,7 +4325,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4320,7 +4335,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4351,10 +4366,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117766609</v>
+        <v>117764762</v>
       </c>
       <c r="B33" t="n">
-        <v>79098</v>
+        <v>8416</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4363,38 +4378,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>688479</v>
+        <v>688452</v>
       </c>
       <c r="R33" t="n">
-        <v>6609210</v>
+        <v>6609271</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4426,7 +4446,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4436,7 +4456,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4467,10 +4487,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117764420</v>
+        <v>117764517</v>
       </c>
       <c r="B34" t="n">
-        <v>8405</v>
+        <v>56499</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4483,42 +4503,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>500 m sso Horssjön (Tärnanområdet), Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>688352</v>
+        <v>688385</v>
       </c>
       <c r="R34" t="n">
-        <v>6609177</v>
+        <v>6609176</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4547,7 +4567,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4557,7 +4577,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4588,10 +4608,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117764562</v>
+        <v>117764129</v>
       </c>
       <c r="B35" t="n">
-        <v>97756</v>
+        <v>96791</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4604,47 +4624,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>688381</v>
+        <v>688355</v>
       </c>
       <c r="R35" t="n">
-        <v>6609183</v>
+        <v>6609075</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4673,7 +4683,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4683,7 +4693,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4714,10 +4724,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117765313</v>
+        <v>117763585</v>
       </c>
       <c r="B36" t="n">
-        <v>78480</v>
+        <v>57303</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4730,34 +4740,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>688449</v>
+        <v>688392</v>
       </c>
       <c r="R36" t="n">
-        <v>6609173</v>
+        <v>6609033</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4789,7 +4804,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4799,7 +4814,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4830,10 +4845,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117764101</v>
+        <v>117763847</v>
       </c>
       <c r="B37" t="n">
-        <v>43657</v>
+        <v>56499</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4846,42 +4861,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>101735</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>500 m sso Horssjön (Tärnanområdet), Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>688365</v>
+        <v>688345</v>
       </c>
       <c r="R37" t="n">
-        <v>6609080</v>
+        <v>6609113</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4910,7 +4925,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4920,7 +4935,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4951,10 +4966,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117764571</v>
+        <v>117765313</v>
       </c>
       <c r="B38" t="n">
-        <v>57303</v>
+        <v>78480</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4967,52 +4982,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>500 m sso Horssjön (Tärnanområdet), Upl</t>
+          <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>688385</v>
+        <v>688449</v>
       </c>
       <c r="R38" t="n">
-        <v>6609183</v>
+        <v>6609173</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5082,10 +5082,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117765426</v>
+        <v>117764300</v>
       </c>
       <c r="B39" t="n">
-        <v>79098</v>
+        <v>96791</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5094,25 +5094,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5122,13 +5122,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>688454</v>
+        <v>688317</v>
       </c>
       <c r="R39" t="n">
-        <v>6609165</v>
+        <v>6609078</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 55825-2023 artfynd.xlsx
+++ b/artfynd/A 55825-2023 artfynd.xlsx
@@ -2784,10 +2784,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117764571</v>
+        <v>117765296</v>
       </c>
       <c r="B20" t="n">
-        <v>57303</v>
+        <v>56500</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2796,41 +2796,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2839,13 +2829,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>688385</v>
+        <v>688444</v>
       </c>
       <c r="R20" t="n">
-        <v>6609183</v>
+        <v>6609199</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2874,7 +2864,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2884,7 +2874,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2915,10 +2905,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117765296</v>
+        <v>117764101</v>
       </c>
       <c r="B21" t="n">
-        <v>56499</v>
+        <v>43657</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2931,42 +2921,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>101735</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>500 m sso Horssjön (Tärnanområdet), Upl</t>
+          <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>688444</v>
+        <v>688365</v>
       </c>
       <c r="R21" t="n">
-        <v>6609199</v>
+        <v>6609080</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2995,7 +2985,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3005,7 +2995,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3036,10 +3026,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117764308</v>
+        <v>117764571</v>
       </c>
       <c r="B22" t="n">
-        <v>8405</v>
+        <v>57304</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3048,46 +3038,56 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>500 m sso Horssjön (Tärnanområdet), Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>688318</v>
+        <v>688385</v>
       </c>
       <c r="R22" t="n">
-        <v>6609079</v>
+        <v>6609183</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3157,10 +3157,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117764531</v>
+        <v>117764308</v>
       </c>
       <c r="B23" t="n">
-        <v>97753</v>
+        <v>8405</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3173,36 +3173,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3211,10 +3202,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>688383</v>
+        <v>688318</v>
       </c>
       <c r="R23" t="n">
-        <v>6609174</v>
+        <v>6609079</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3246,7 +3237,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3256,7 +3247,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3287,10 +3278,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117764382</v>
+        <v>117764129</v>
       </c>
       <c r="B24" t="n">
-        <v>90499</v>
+        <v>96793</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3299,25 +3290,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3327,10 +3318,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>688339</v>
+        <v>688355</v>
       </c>
       <c r="R24" t="n">
-        <v>6609152</v>
+        <v>6609075</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3362,7 +3353,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3372,7 +3363,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3403,10 +3394,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117764101</v>
+        <v>117763847</v>
       </c>
       <c r="B25" t="n">
-        <v>43657</v>
+        <v>56500</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3419,42 +3410,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101735</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>500 m sso Horssjön (Tärnanområdet), Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>688365</v>
+        <v>688345</v>
       </c>
       <c r="R25" t="n">
-        <v>6609080</v>
+        <v>6609113</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3483,7 +3474,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3493,7 +3484,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3524,10 +3515,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117765426</v>
+        <v>117764531</v>
       </c>
       <c r="B26" t="n">
-        <v>79098</v>
+        <v>97755</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3536,41 +3527,55 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>688454</v>
+        <v>688383</v>
       </c>
       <c r="R26" t="n">
-        <v>6609165</v>
+        <v>6609174</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3599,7 +3604,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3609,7 +3614,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3640,10 +3645,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117764420</v>
+        <v>117765426</v>
       </c>
       <c r="B27" t="n">
-        <v>8405</v>
+        <v>79100</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3652,46 +3657,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106554</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>688352</v>
+        <v>688454</v>
       </c>
       <c r="R27" t="n">
-        <v>6609177</v>
+        <v>6609165</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3761,10 +3761,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117766609</v>
+        <v>117764161</v>
       </c>
       <c r="B28" t="n">
-        <v>79098</v>
+        <v>57304</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3777,34 +3777,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>688479</v>
+        <v>688348</v>
       </c>
       <c r="R28" t="n">
-        <v>6609210</v>
+        <v>6609056</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3836,7 +3841,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3846,7 +3851,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3877,10 +3882,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117764465</v>
+        <v>117765313</v>
       </c>
       <c r="B29" t="n">
-        <v>8416</v>
+        <v>78482</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3889,43 +3894,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>688352</v>
+        <v>688449</v>
       </c>
       <c r="R29" t="n">
-        <v>6609177</v>
+        <v>6609173</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3998,10 +3998,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117763595</v>
+        <v>117764300</v>
       </c>
       <c r="B30" t="n">
-        <v>8416</v>
+        <v>96793</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4014,39 +4014,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>688398</v>
+        <v>688317</v>
       </c>
       <c r="R30" t="n">
-        <v>6609030</v>
+        <v>6609078</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4078,7 +4073,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4088,7 +4083,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4119,10 +4114,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117764562</v>
+        <v>117764517</v>
       </c>
       <c r="B31" t="n">
-        <v>97756</v>
+        <v>56500</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4135,47 +4130,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223597</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>500 m sso Horssjön (Tärnanområdet), Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>688381</v>
+        <v>688385</v>
       </c>
       <c r="R31" t="n">
-        <v>6609183</v>
+        <v>6609176</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4204,7 +4194,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4214,7 +4204,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4245,10 +4235,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117764161</v>
+        <v>117764562</v>
       </c>
       <c r="B32" t="n">
-        <v>57303</v>
+        <v>97758</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4257,31 +4247,36 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>223597</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4290,13 +4285,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>688348</v>
+        <v>688381</v>
       </c>
       <c r="R32" t="n">
-        <v>6609056</v>
+        <v>6609183</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4325,7 +4320,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4335,7 +4330,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4366,7 +4361,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117764762</v>
+        <v>117764465</v>
       </c>
       <c r="B33" t="n">
         <v>8416</v>
@@ -4411,10 +4406,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>688452</v>
+        <v>688352</v>
       </c>
       <c r="R33" t="n">
-        <v>6609271</v>
+        <v>6609177</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4446,7 +4441,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4456,7 +4451,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4487,10 +4482,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117764517</v>
+        <v>117766609</v>
       </c>
       <c r="B34" t="n">
-        <v>56499</v>
+        <v>79100</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4499,46 +4494,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>500 m sso Horssjön (Tärnanområdet), Upl</t>
+          <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>688385</v>
+        <v>688479</v>
       </c>
       <c r="R34" t="n">
-        <v>6609176</v>
+        <v>6609210</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4567,7 +4557,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4577,7 +4567,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4608,10 +4598,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117764129</v>
+        <v>117763585</v>
       </c>
       <c r="B35" t="n">
-        <v>96791</v>
+        <v>57304</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4620,38 +4610,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>688355</v>
+        <v>688392</v>
       </c>
       <c r="R35" t="n">
-        <v>6609075</v>
+        <v>6609033</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4683,7 +4678,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4693,7 +4688,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4724,10 +4719,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117763585</v>
+        <v>117764420</v>
       </c>
       <c r="B36" t="n">
-        <v>57303</v>
+        <v>8405</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4736,31 +4731,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4769,10 +4764,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>688392</v>
+        <v>688352</v>
       </c>
       <c r="R36" t="n">
-        <v>6609033</v>
+        <v>6609177</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4804,7 +4799,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4814,7 +4809,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4845,10 +4840,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117763847</v>
+        <v>117764762</v>
       </c>
       <c r="B37" t="n">
-        <v>56499</v>
+        <v>8416</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4861,42 +4856,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>500 m sso Horssjön (Tärnanområdet), Upl</t>
+          <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>688345</v>
+        <v>688452</v>
       </c>
       <c r="R37" t="n">
-        <v>6609113</v>
+        <v>6609271</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4925,7 +4920,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4935,7 +4930,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4966,10 +4961,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117765313</v>
+        <v>117764382</v>
       </c>
       <c r="B38" t="n">
-        <v>78480</v>
+        <v>90501</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4982,21 +4977,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5006,10 +5001,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>688449</v>
+        <v>688339</v>
       </c>
       <c r="R38" t="n">
-        <v>6609173</v>
+        <v>6609152</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -5041,7 +5036,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5051,7 +5046,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5082,10 +5077,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117764300</v>
+        <v>117763595</v>
       </c>
       <c r="B39" t="n">
-        <v>96791</v>
+        <v>8416</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5098,34 +5093,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sjöberg (Sjöberg), Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>688317</v>
+        <v>688398</v>
       </c>
       <c r="R39" t="n">
-        <v>6609078</v>
+        <v>6609030</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 55825-2023 artfynd.xlsx
+++ b/artfynd/A 55825-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113190394</v>
+        <v>113400565</v>
       </c>
       <c r="B2" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordöst Lilla Harsjön (Nordöst Lilla Harsjön), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688415</v>
+        <v>688328</v>
       </c>
       <c r="R2" t="n">
-        <v>6609092</v>
+        <v>6609144</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,31 +767,46 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mattias Ödevidh</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mattias Ödevidh</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113190191</v>
+        <v>117764382</v>
       </c>
       <c r="B3" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,43 +814,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nordöst Lilla Harsjön 5 (Nordöst Lilla Harsjön 5), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688446</v>
+        <v>688339</v>
       </c>
       <c r="R3" t="n">
-        <v>6609033</v>
+        <v>6609152</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,22 +868,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,68 +898,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mattias Ödevidh</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Ödevidh</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113190450</v>
+        <v>61021899</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nordöst Lilla Harsjön (Nordöst Lilla Harsjön), Upl</t>
+          <t>Lilla Harsjön, NNO om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>688402</v>
+        <v>688512</v>
       </c>
       <c r="R4" t="n">
-        <v>6609093</v>
+        <v>6609263</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,22 +982,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2016-08-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2016-08-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal tallåga. Gammal flerskiktad barrblandskog. Enstaka gammal asp, björk och senvuxen ek. Tämligen orörd karaktär med inslag av död ved. Delvis hänglavsrika partier med insprängda sumpskogspartier. Intressant kryptogamflora.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,27 +1007,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mattias Ödevidh</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Ödevidh</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113399689</v>
+        <v>113190178</v>
       </c>
       <c r="B5" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,43 +1030,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Nordöst Lilla Harsjön 5, Nordöst Lilla Harsjön 5, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>688457</v>
+        <v>688447</v>
       </c>
       <c r="R5" t="n">
-        <v>6609272</v>
+        <v>6609014</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,22 +1085,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,27 +1115,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Mattias Ödevidh</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Mattias Ödevidh</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113399890</v>
+        <v>113400066</v>
       </c>
       <c r="B6" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,43 +1138,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>4217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>688404</v>
+        <v>688427</v>
       </c>
       <c r="R6" t="n">
-        <v>6609034</v>
+        <v>6609027</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,6 +1219,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1260,15 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113400068</v>
+        <v>61015892</v>
       </c>
       <c r="B7" t="n">
-        <v>90726</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,38 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Lilla Harsjön, NNO om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>688427</v>
+        <v>688391</v>
       </c>
       <c r="R7" t="n">
-        <v>6609027</v>
+        <v>6608972</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,22 +1322,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:41</t>
+          <t>2016-08-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:41</t>
+          <t>2016-08-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,53 +1336,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113399902</v>
+        <v>113190149</v>
       </c>
       <c r="B8" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,43 +1366,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Nordöst Lilla Harsjön 5, Nordöst Lilla Harsjön 5, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>688404</v>
+        <v>688445</v>
       </c>
       <c r="R8" t="n">
-        <v>6609043</v>
+        <v>6608999</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,22 +1421,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,27 +1451,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Mattias Ödevidh</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Mattias Ödevidh</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399897</v>
+        <v>113400073</v>
       </c>
       <c r="B9" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,40 +1474,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>688401</v>
+        <v>688432</v>
       </c>
       <c r="R9" t="n">
-        <v>6609043</v>
+        <v>6609049</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1592,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,15 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113400073</v>
+        <v>113400418</v>
       </c>
       <c r="B10" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,17 +1603,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>688432</v>
+        <v>688381</v>
       </c>
       <c r="R10" t="n">
-        <v>6609049</v>
+        <v>6609221</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1705,7 +1642,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1652,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,51 +1679,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113400228</v>
+        <v>113400175</v>
       </c>
       <c r="B11" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>688432</v>
+        <v>688451</v>
       </c>
       <c r="R11" t="n">
-        <v>6609177</v>
+        <v>6609118</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1818,7 +1750,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1828,7 +1760,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,51 +1787,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113400403</v>
+        <v>117765313</v>
       </c>
       <c r="B12" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>688373</v>
+        <v>688449</v>
       </c>
       <c r="R12" t="n">
-        <v>6609243</v>
+        <v>6609173</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1926,22 +1852,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,19 +1890,18 @@
           <t>Martin Permats</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113400305</v>
+        <v>113400228</v>
       </c>
       <c r="B13" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2005,14 +1930,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>688475</v>
+        <v>688432</v>
       </c>
       <c r="R13" t="n">
-        <v>6609209</v>
+        <v>6609177</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2044,7 +1969,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2054,7 +1979,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2084,12 +2009,7 @@
         <v>113400296</v>
       </c>
       <c r="B14" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2038,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -2194,15 +2114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113400565</v>
+        <v>113400305</v>
       </c>
       <c r="B15" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,35 +2125,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>688328</v>
+        <v>688475</v>
       </c>
       <c r="R15" t="n">
-        <v>6609144</v>
+        <v>6609209</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2270,7 +2185,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,7 +2195,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,26 +2206,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2327,15 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113400175</v>
+        <v>113400403</v>
       </c>
       <c r="B16" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,35 +2233,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>688451</v>
+        <v>688373</v>
       </c>
       <c r="R16" t="n">
-        <v>6609118</v>
+        <v>6609243</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2403,7 +2293,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2413,7 +2303,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2440,59 +2330,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399808</v>
+        <v>117765426</v>
       </c>
       <c r="B17" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>688415</v>
+        <v>688454</v>
       </c>
       <c r="R17" t="n">
-        <v>6609177</v>
+        <v>6609165</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2516,22 +2395,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2554,55 +2433,53 @@
           <t>Martin Permats</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113400418</v>
+        <v>117766609</v>
       </c>
       <c r="B18" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>688381</v>
+        <v>688479</v>
       </c>
       <c r="R18" t="n">
-        <v>6609221</v>
+        <v>6609210</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2629,22 +2506,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2667,58 +2544,56 @@
           <t>Martin Permats</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113400103</v>
+        <v>117766912</v>
       </c>
       <c r="B19" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>688413</v>
+        <v>688485</v>
       </c>
       <c r="R19" t="n">
-        <v>6609099</v>
+        <v>6609185</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2742,22 +2617,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2780,19 +2655,18 @@
           <t>Martin Permats</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117764420</v>
+        <v>113190450</v>
       </c>
       <c r="B20" t="n">
-        <v>8405</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2800,42 +2674,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Nordöst Lilla Harsjön, Nordöst Lilla Harsjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>688352</v>
+        <v>688402</v>
       </c>
       <c r="R20" t="n">
-        <v>6609177</v>
+        <v>6609093</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2859,22 +2734,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2889,31 +2764,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Mattias Ödevidh</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117765296</v>
+        <v>117763585</v>
       </c>
       <c r="B21" t="n">
-        <v>56502</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2921,42 +2787,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>500 m sso Horssjön (Tärnanområdet), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>688444</v>
+        <v>688392</v>
       </c>
       <c r="R21" t="n">
-        <v>6609199</v>
+        <v>6609033</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2985,7 +2851,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2995,7 +2861,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3026,15 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117763847</v>
+        <v>117764161</v>
       </c>
       <c r="B22" t="n">
-        <v>56502</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3042,42 +2903,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>500 m sso Horssjön (Tärnanområdet), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>688345</v>
+        <v>688348</v>
       </c>
       <c r="R22" t="n">
-        <v>6609113</v>
+        <v>6609056</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3106,7 +2967,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3116,7 +2977,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3147,15 +3008,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117764129</v>
+        <v>117764571</v>
       </c>
       <c r="B23" t="n">
-        <v>96795</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,37 +3019,52 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>500 m sso Horssjön, Tärnanområdet, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>688355</v>
+        <v>688385</v>
       </c>
       <c r="R23" t="n">
-        <v>6609075</v>
+        <v>6609183</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3222,7 +3093,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3232,7 +3103,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3263,15 +3134,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117764300</v>
+        <v>117763847</v>
       </c>
       <c r="B24" t="n">
-        <v>96795</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,37 +3145,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>500 m sso Horssjön, Tärnanområdet, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>688317</v>
+        <v>688345</v>
       </c>
       <c r="R24" t="n">
-        <v>6609078</v>
+        <v>6609113</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3338,7 +3209,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3348,7 +3219,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3379,15 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117764762</v>
+        <v>117764517</v>
       </c>
       <c r="B25" t="n">
-        <v>8416</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3395,42 +3261,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>500 m sso Horssjön, Tärnanområdet, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>688452</v>
+        <v>688385</v>
       </c>
       <c r="R25" t="n">
-        <v>6609271</v>
+        <v>6609176</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3459,7 +3325,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3469,7 +3335,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3500,15 +3366,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117764517</v>
+        <v>117765296</v>
       </c>
       <c r="B26" t="n">
-        <v>56502</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3541,14 +3402,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>500 m sso Horssjön (Tärnanområdet), Upl</t>
+          <t>500 m sso Horssjön, Tärnanområdet, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>688385</v>
+        <v>688444</v>
       </c>
       <c r="R26" t="n">
-        <v>6609176</v>
+        <v>6609199</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3580,7 +3441,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3590,7 +3451,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3621,50 +3482,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117764382</v>
+        <v>117764101</v>
       </c>
       <c r="B27" t="n">
-        <v>90503</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>101735</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>688339</v>
+        <v>688365</v>
       </c>
       <c r="R27" t="n">
-        <v>6609152</v>
+        <v>6609080</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3696,7 +3557,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3706,7 +3567,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3737,15 +3598,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117765426</v>
+        <v>113190191</v>
       </c>
       <c r="B28" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3753,37 +3609,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Nordöst Lilla Harsjön 5, Nordöst Lilla Harsjön 5, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>688454</v>
+        <v>688446</v>
       </c>
       <c r="R28" t="n">
-        <v>6609165</v>
+        <v>6609033</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3807,22 +3669,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3837,74 +3699,61 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Mattias Ödevidh</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117764161</v>
+        <v>113190394</v>
       </c>
       <c r="B29" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Nordöst Lilla Harsjön, Nordöst Lilla Harsjön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>688348</v>
+        <v>688415</v>
       </c>
       <c r="R29" t="n">
-        <v>6609056</v>
+        <v>6609092</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3928,22 +3777,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3958,84 +3807,66 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Mattias Ödevidh</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+          <t>Mattias Ödevidh</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117764571</v>
+        <v>113399689</v>
       </c>
       <c r="B30" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>500 m sso Horssjön (Tärnanområdet), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>688385</v>
+        <v>688457</v>
       </c>
       <c r="R30" t="n">
-        <v>6609183</v>
+        <v>6609272</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4059,22 +3890,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4097,23 +3928,14 @@
           <t>Martin Permats</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117764531</v>
+        <v>113399808</v>
       </c>
       <c r="B31" t="n">
-        <v>97757</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4121,48 +3943,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>688383</v>
+        <v>688415</v>
       </c>
       <c r="R31" t="n">
-        <v>6609174</v>
+        <v>6609177</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4189,22 +4003,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4227,63 +4041,55 @@
           <t>Martin Permats</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117763585</v>
+        <v>113399890</v>
       </c>
       <c r="B32" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>688392</v>
+        <v>688404</v>
       </c>
       <c r="R32" t="n">
-        <v>6609033</v>
+        <v>6609034</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4310,22 +4116,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4348,23 +4154,14 @@
           <t>Martin Permats</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117764562</v>
+        <v>113399896</v>
       </c>
       <c r="B33" t="n">
-        <v>97760</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4372,47 +4169,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223597</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>688381</v>
+        <v>688401</v>
       </c>
       <c r="R33" t="n">
-        <v>6609183</v>
+        <v>6609043</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4436,22 +4229,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4474,23 +4267,14 @@
           <t>Martin Permats</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117764465</v>
+        <v>113399899</v>
       </c>
       <c r="B34" t="n">
-        <v>8416</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4516,6 +4300,7 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>färska gnagspår</t>
@@ -4523,17 +4308,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>688352</v>
+        <v>688404</v>
       </c>
       <c r="R34" t="n">
-        <v>6609177</v>
+        <v>6609043</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4557,22 +4342,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4595,23 +4380,14 @@
           <t>Martin Permats</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117764101</v>
+        <v>113400103</v>
       </c>
       <c r="B35" t="n">
-        <v>43659</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4619,42 +4395,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101735</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>688365</v>
+        <v>688413</v>
       </c>
       <c r="R35" t="n">
-        <v>6609080</v>
+        <v>6609099</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4678,22 +4450,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4716,23 +4488,14 @@
           <t>Martin Permats</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>117763595</v>
       </c>
       <c r="B36" t="n">
-        <v>8416</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4765,7 +4528,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -4845,15 +4608,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117764308</v>
+        <v>117764465</v>
       </c>
       <c r="B37" t="n">
-        <v>8405</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4861,39 +4619,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>688318</v>
+        <v>688352</v>
       </c>
       <c r="R37" t="n">
-        <v>6609079</v>
+        <v>6609177</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4925,7 +4683,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4935,7 +4693,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4966,50 +4724,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117766609</v>
+        <v>117764762</v>
       </c>
       <c r="B38" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>688479</v>
+        <v>688452</v>
       </c>
       <c r="R38" t="n">
-        <v>6609210</v>
+        <v>6609271</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -5041,7 +4799,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5051,7 +4809,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5082,50 +4840,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117765313</v>
+        <v>117764308</v>
       </c>
       <c r="B39" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sjöberg (Sjöberg), Upl</t>
+          <t>Sjöberg, Sjöberg, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>688449</v>
+        <v>688318</v>
       </c>
       <c r="R39" t="n">
-        <v>6609173</v>
+        <v>6609079</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5157,7 +4915,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5167,7 +4925,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5191,6 +4949,918 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>117764420</v>
+      </c>
+      <c r="B40" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sjöberg, Sjöberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>688352</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6609177</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>117764531</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sjöberg, Sjöberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>688383</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6609174</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>95828400</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L Harsjön, 850 m NNO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>688515</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6609218</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Mossrik skog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>117764129</v>
+      </c>
+      <c r="B43" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Sjöberg, Sjöberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>688355</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6609075</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>117764300</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sjöberg, Sjöberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>688317</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6609078</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>119451922</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lilla Harsjön, Lilla Harsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>688397</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6608974</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>119451867</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 500m nordost om Harsjön, Sjöberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>688393</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6608971</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>117764562</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sjöberg, Sjöberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>688381</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6609183</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
         <is>
           <t>Nya Tärnan gruppen</t>
         </is>
